--- a/monolith-to-microservice-architecture-uionly-stack-a-b-c/microservice-architecture/microservice-architecture-update-02022026.xlsx
+++ b/monolith-to-microservice-architecture-uionly-stack-a-b-c/microservice-architecture/microservice-architecture-update-02022026.xlsx
@@ -5,17 +5,18 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WiN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\monolith-to-microservice-architecture-uionly-stack-a-b-c\microservice-architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21C7E075-90FA-4EC8-BC07-7F60D9A19F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B1BCD0-28BB-48FA-A0EA-82F94E3E28B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MicroServ Arch" sheetId="1" r:id="rId1"/>
     <sheet name="InterService Commu" sheetId="2" r:id="rId2"/>
     <sheet name="MicroServ Arch_simple" sheetId="3" r:id="rId3"/>
+    <sheet name="MicroServ Arch_simple_updated" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="247">
   <si>
     <t>Part</t>
   </si>
@@ -865,6 +866,59 @@
   </si>
   <si>
     <t>Python Txtai</t>
+  </si>
+  <si>
+    <t>Note : a) Part 1 is just production environment preparation and setup (Not include here)</t>
+  </si>
+  <si>
+    <t>Authentication - Frontend Stack</t>
+  </si>
+  <si>
+    <t>Authentication - Backend Stack</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mql5 (EA)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for market data fetching from MT5 terminals + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Python Stacks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for Retry/Recover/Resend machanism</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1176,7 +1230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1293,11 +1347,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1485,6 +1548,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1545,44 +1641,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2192,45 +2288,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="G1" s="73" t="s">
+      <c r="G1" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.6">
       <c r="G4" s="6" t="s">
@@ -2339,21 +2435,21 @@
       <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="1:17" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="80"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="91"/>
       <c r="F10" s="37"/>
-      <c r="G10" s="81" t="s">
+      <c r="G10" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="83"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="94"/>
       <c r="L10" s="30"/>
       <c r="M10" s="29"/>
       <c r="N10" s="3"/>
@@ -3328,19 +3424,19 @@
       </c>
     </row>
     <row r="31" spans="1:17" s="11" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="74" t="s">
+      <c r="A31" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="76" t="s">
+      <c r="C31" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="D31" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="76" t="s">
+      <c r="E31" s="87" t="s">
         <v>133</v>
       </c>
       <c r="F31" s="40"/>
@@ -3363,11 +3459,11 @@
       <c r="Q31" s="18"/>
     </row>
     <row r="32" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="74"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
       <c r="F32" s="40"/>
       <c r="G32" s="7" t="s">
         <v>81</v>
@@ -3388,11 +3484,11 @@
       <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="74"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
+      <c r="A33" s="85"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
       <c r="F33" s="40"/>
       <c r="G33" s="7" t="s">
         <v>83</v>
@@ -3413,11 +3509,11 @@
       <c r="Q33" s="18"/>
     </row>
     <row r="34" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="74"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
       <c r="F34" s="40"/>
       <c r="G34" s="7" t="s">
         <v>87</v>
@@ -3438,11 +3534,11 @@
       <c r="Q34" s="18"/>
     </row>
     <row r="35" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="74"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
       <c r="F35" s="40"/>
       <c r="G35" s="7" t="s">
         <v>118</v>
@@ -3463,11 +3559,11 @@
       <c r="Q35" s="18"/>
     </row>
     <row r="36" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="74"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="89"/>
+      <c r="E36" s="89"/>
       <c r="F36" s="41"/>
       <c r="G36" s="7" t="s">
         <v>108</v>
@@ -4867,45 +4963,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
-      <c r="G1" s="73" t="s">
+      <c r="G1" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
     </row>
     <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
     </row>
     <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
       <c r="G4" s="6" t="s">
@@ -5014,21 +5110,21 @@
       <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="1:17" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="80"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="91"/>
       <c r="F10" s="37"/>
-      <c r="G10" s="81" t="s">
+      <c r="G10" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="83"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="94"/>
       <c r="L10" s="30"/>
       <c r="M10" s="29"/>
       <c r="N10" s="3"/>
@@ -5082,7 +5178,7 @@
       <c r="B12" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C12" s="93" t="s">
+      <c r="C12" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="7" t="s">
@@ -5098,7 +5194,7 @@
       <c r="H12" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="I12" s="93" t="s">
+      <c r="I12" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J12" s="43" t="s">
@@ -5131,7 +5227,7 @@
       <c r="B13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="93" t="s">
+      <c r="C13" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -5147,7 +5243,7 @@
       <c r="H13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="96" t="s">
+      <c r="I13" s="74" t="s">
         <v>122</v>
       </c>
       <c r="J13" s="9" t="s">
@@ -5178,7 +5274,7 @@
       <c r="B14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="93" t="s">
+      <c r="C14" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -5194,7 +5290,7 @@
       <c r="H14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="93" t="s">
+      <c r="I14" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J14" s="9" t="s">
@@ -5221,19 +5317,19 @@
       </c>
     </row>
     <row r="15" spans="1:17" s="11" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="89" t="s">
+      <c r="A15" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="89" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="89" t="s">
+      <c r="C15" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="100" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="100" t="s">
         <v>233</v>
       </c>
       <c r="F15" s="39"/>
@@ -5243,7 +5339,7 @@
       <c r="H15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="97" t="s">
+      <c r="I15" s="75" t="s">
         <v>223</v>
       </c>
       <c r="J15" s="9" t="s">
@@ -5270,11 +5366,11 @@
       </c>
     </row>
     <row r="16" spans="1:17" s="11" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="90"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
       <c r="F16" s="39"/>
       <c r="G16" s="7" t="s">
         <v>15</v>
@@ -5282,7 +5378,7 @@
       <c r="H16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="98" t="s">
+      <c r="I16" s="76" t="s">
         <v>229</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -5305,7 +5401,7 @@
       <c r="B17" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D17" s="7" t="s">
@@ -5321,7 +5417,7 @@
       <c r="H17" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="93" t="s">
+      <c r="I17" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J17" s="43" t="s">
@@ -5354,7 +5450,7 @@
       <c r="B18" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -5370,7 +5466,7 @@
       <c r="H18" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="93" t="s">
+      <c r="I18" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J18" s="9" t="s">
@@ -5403,7 +5499,7 @@
       <c r="B19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="93" t="s">
+      <c r="C19" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D19" s="7" t="s">
@@ -5419,7 +5515,7 @@
       <c r="H19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I19" s="93" t="s">
+      <c r="I19" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J19" s="9" t="s">
@@ -5452,7 +5548,7 @@
       <c r="B20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -5468,7 +5564,7 @@
       <c r="H20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I20" s="93" t="s">
+      <c r="I20" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J20" s="9" t="s">
@@ -5501,7 +5597,7 @@
       <c r="B21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="93" t="s">
+      <c r="C21" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D21" s="7" t="s">
@@ -5517,7 +5613,7 @@
       <c r="H21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="93" t="s">
+      <c r="I21" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J21" s="9" t="s">
@@ -5550,7 +5646,7 @@
       <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C22" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D22" s="7" t="s">
@@ -5566,7 +5662,7 @@
       <c r="H22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I22" s="93" t="s">
+      <c r="I22" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J22" s="9" t="s">
@@ -5599,7 +5695,7 @@
       <c r="B23" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="93" t="s">
+      <c r="C23" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -5615,7 +5711,7 @@
       <c r="H23" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="93" t="s">
+      <c r="I23" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J23" s="9" t="s">
@@ -5648,7 +5744,7 @@
       <c r="B24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="93" t="s">
+      <c r="C24" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D24" s="7" t="s">
@@ -5664,7 +5760,7 @@
       <c r="H24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I24" s="93" t="s">
+      <c r="I24" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J24" s="9" t="s">
@@ -5697,7 +5793,7 @@
       <c r="B25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="93" t="s">
+      <c r="C25" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D25" s="7" t="s">
@@ -5713,7 +5809,7 @@
       <c r="H25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="93" t="s">
+      <c r="I25" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J25" s="9" t="s">
@@ -5746,7 +5842,7 @@
       <c r="B26" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="93" t="s">
+      <c r="C26" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D26" s="7" t="s">
@@ -5762,7 +5858,7 @@
       <c r="H26" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="I26" s="93" t="s">
+      <c r="I26" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J26" s="9" t="s">
@@ -5795,7 +5891,7 @@
       <c r="B27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D27" s="7" t="s">
@@ -5811,7 +5907,7 @@
       <c r="H27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="93" t="s">
+      <c r="I27" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J27" s="9" t="s">
@@ -5844,7 +5940,7 @@
       <c r="B28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="93" t="s">
+      <c r="C28" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D28" s="7" t="s">
@@ -5860,7 +5956,7 @@
       <c r="H28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="93" t="s">
+      <c r="I28" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J28" s="9" t="s">
@@ -5893,7 +5989,7 @@
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="93" t="s">
+      <c r="C29" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D29" s="7" t="s">
@@ -5909,7 +6005,7 @@
       <c r="H29" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I29" s="93" t="s">
+      <c r="I29" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J29" s="9" t="s">
@@ -5940,7 +6036,7 @@
       <c r="B30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="93" t="s">
+      <c r="C30" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D30" s="7" t="s">
@@ -5956,7 +6052,7 @@
       <c r="H30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="93" t="s">
+      <c r="I30" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J30" s="9" t="s">
@@ -5989,7 +6085,7 @@
       <c r="B31" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="93" t="s">
+      <c r="C31" s="73" t="s">
         <v>97</v>
       </c>
       <c r="D31" s="7" t="s">
@@ -6005,7 +6101,7 @@
       <c r="H31" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I31" s="93" t="s">
+      <c r="I31" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J31" s="9" t="s">
@@ -6032,19 +6128,19 @@
       </c>
     </row>
     <row r="32" spans="1:17" s="11" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="84" t="s">
+      <c r="A32" s="95" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="85" t="s">
+      <c r="B32" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="86" t="s">
+      <c r="C32" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="86" t="s">
+      <c r="D32" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="86" t="s">
+      <c r="E32" s="97" t="s">
         <v>133</v>
       </c>
       <c r="F32" s="40"/>
@@ -6054,7 +6150,7 @@
       <c r="H32" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="99" t="s">
+      <c r="I32" s="77" t="s">
         <v>84</v>
       </c>
       <c r="J32" s="9" t="s">
@@ -6067,11 +6163,11 @@
       <c r="Q32" s="18"/>
     </row>
     <row r="33" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="84"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="87"/>
+      <c r="A33" s="95"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
       <c r="F33" s="40"/>
       <c r="G33" s="7" t="s">
         <v>81</v>
@@ -6079,7 +6175,7 @@
       <c r="H33" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="I33" s="99" t="s">
+      <c r="I33" s="77" t="s">
         <v>84</v>
       </c>
       <c r="J33" s="9" t="s">
@@ -6092,11 +6188,11 @@
       <c r="Q33" s="18"/>
     </row>
     <row r="34" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="84"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
+      <c r="A34" s="95"/>
+      <c r="B34" s="96"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
       <c r="F34" s="40"/>
       <c r="G34" s="7" t="s">
         <v>83</v>
@@ -6104,7 +6200,7 @@
       <c r="H34" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I34" s="99" t="s">
+      <c r="I34" s="77" t="s">
         <v>84</v>
       </c>
       <c r="J34" s="9" t="s">
@@ -6117,11 +6213,11 @@
       <c r="Q34" s="18"/>
     </row>
     <row r="35" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="84"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="87"/>
-      <c r="D35" s="87"/>
-      <c r="E35" s="87"/>
+      <c r="A35" s="95"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
       <c r="F35" s="40"/>
       <c r="G35" s="7" t="s">
         <v>87</v>
@@ -6129,7 +6225,7 @@
       <c r="H35" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="I35" s="99" t="s">
+      <c r="I35" s="77" t="s">
         <v>84</v>
       </c>
       <c r="J35" s="9" t="s">
@@ -6142,11 +6238,11 @@
       <c r="Q35" s="18"/>
     </row>
     <row r="36" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="84"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="87"/>
-      <c r="D36" s="87"/>
-      <c r="E36" s="87"/>
+      <c r="A36" s="95"/>
+      <c r="B36" s="96"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98"/>
       <c r="F36" s="40"/>
       <c r="G36" s="7" t="s">
         <v>118</v>
@@ -6154,7 +6250,7 @@
       <c r="H36" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I36" s="99" t="s">
+      <c r="I36" s="77" t="s">
         <v>84</v>
       </c>
       <c r="J36" s="9" t="s">
@@ -6167,11 +6263,11 @@
       <c r="Q36" s="18"/>
     </row>
     <row r="37" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="84"/>
-      <c r="B37" s="85"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
+      <c r="A37" s="95"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
       <c r="F37" s="41"/>
       <c r="G37" s="7" t="s">
         <v>108</v>
@@ -6179,7 +6275,7 @@
       <c r="H37" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="I37" s="100" t="s">
+      <c r="I37" s="78" t="s">
         <v>86</v>
       </c>
       <c r="J37" s="9" t="s">
@@ -6204,13 +6300,13 @@
       <c r="H38" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="I38" s="101" t="s">
+      <c r="I38" s="79" t="s">
         <v>223</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="K38" s="105" t="s">
+      <c r="K38" s="83" t="s">
         <v>128</v>
       </c>
       <c r="L38" s="12"/>
@@ -6229,10 +6325,10 @@
       <c r="H39" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="102" t="s">
+      <c r="I39" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="J39" s="104" t="s">
+      <c r="J39" s="82" t="s">
         <v>242</v>
       </c>
       <c r="K39" s="13" t="s">
@@ -6254,7 +6350,7 @@
       <c r="H40" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="I40" s="103" t="s">
+      <c r="I40" s="81" t="s">
         <v>224</v>
       </c>
       <c r="J40" s="13" t="s">
@@ -6268,7 +6364,7 @@
     </row>
     <row r="41" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A41" s="54" t="s">
-        <v>110</v>
+        <v>243</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
@@ -6312,4 +6408,1321 @@
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D501F09-0F51-4028-AA61-070B2DDA5F82}">
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="2" max="2" width="28.3984375" customWidth="1"/>
+    <col min="3" max="5" width="12.8984375" customWidth="1"/>
+    <col min="6" max="6" width="0.6484375" customWidth="1"/>
+    <col min="7" max="7" width="7.34765625" customWidth="1"/>
+    <col min="8" max="8" width="32.59765625" customWidth="1"/>
+    <col min="9" max="9" width="13.75" customWidth="1"/>
+    <col min="10" max="10" width="32.69921875" customWidth="1"/>
+    <col min="11" max="11" width="13.6484375" customWidth="1"/>
+    <col min="12" max="12" width="23.546875" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.94921875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="75.19921875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="5.75" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="81.25" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="5.796875" style="1" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+      <c r="G1" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="84"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+    </row>
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+      <c r="G4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="90" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="92" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="38"/>
+      <c r="G11" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" s="31"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
+    </row>
+    <row r="12" spans="1:17" s="11" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I12" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J12" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="L12" s="32"/>
+      <c r="M12" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="11" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L14" s="33"/>
+      <c r="M14" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="11" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="100" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="100" t="s">
+        <v>233</v>
+      </c>
+      <c r="F15" s="39"/>
+      <c r="G15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="I15" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="L15" s="33"/>
+      <c r="M15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="11" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="101"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="I16" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L16" s="33"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F17" s="39"/>
+      <c r="G17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L17" s="33"/>
+      <c r="M17" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F18" s="39"/>
+      <c r="G18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L18" s="33"/>
+      <c r="M18" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L19" s="33"/>
+      <c r="M19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="O19" s="7">
+        <v>3</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F20" s="39"/>
+      <c r="G20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L20" s="33"/>
+      <c r="M20" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="O20" s="7">
+        <v>2</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="11" customFormat="1" ht="21.3" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" s="39"/>
+      <c r="G21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L21" s="33"/>
+      <c r="M21" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" s="39"/>
+      <c r="G22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L22" s="33"/>
+      <c r="M22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F23" s="39"/>
+      <c r="G23" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L23" s="33"/>
+      <c r="M23" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q23" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F24" s="39"/>
+      <c r="G24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L24" s="33"/>
+      <c r="M24" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="39"/>
+      <c r="G25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L25" s="33"/>
+      <c r="M25" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="O25" s="17">
+        <v>3</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" s="39"/>
+      <c r="G26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I26" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L26" s="33"/>
+      <c r="M26" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" s="39"/>
+      <c r="G27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L27" s="33"/>
+      <c r="M27" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" s="39"/>
+      <c r="G28" s="114" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="115" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="116" t="s">
+        <v>222</v>
+      </c>
+      <c r="J28" s="115" t="s">
+        <v>238</v>
+      </c>
+      <c r="K28" s="115" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" s="33"/>
+      <c r="M28" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F29" s="39"/>
+      <c r="G29" s="114" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="115" t="s">
+        <v>63</v>
+      </c>
+      <c r="I29" s="116" t="s">
+        <v>222</v>
+      </c>
+      <c r="J29" s="115" t="s">
+        <v>238</v>
+      </c>
+      <c r="K29" s="115" t="s">
+        <v>126</v>
+      </c>
+      <c r="L29" s="33"/>
+      <c r="M29" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" s="7"/>
+      <c r="P29" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F30" s="39"/>
+      <c r="G30" s="114" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="115" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="116" t="s">
+        <v>222</v>
+      </c>
+      <c r="J30" s="115" t="s">
+        <v>238</v>
+      </c>
+      <c r="K30" s="115" t="s">
+        <v>126</v>
+      </c>
+      <c r="L30" s="33"/>
+      <c r="M30" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="11" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" s="39"/>
+      <c r="G31" s="114" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="115" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="116" t="s">
+        <v>222</v>
+      </c>
+      <c r="J31" s="115" t="s">
+        <v>238</v>
+      </c>
+      <c r="K31" s="115" t="s">
+        <v>126</v>
+      </c>
+      <c r="L31" s="33"/>
+      <c r="M31" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="O31" s="7">
+        <v>0</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="11" customFormat="1" ht="27.3" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="108"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="109"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="106"/>
+      <c r="G32" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="I32" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L32" s="12"/>
+      <c r="Q32" s="18"/>
+    </row>
+    <row r="33" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="108"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="Q33" s="18"/>
+    </row>
+    <row r="34" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="51"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I34" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="K34" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="L34" s="12"/>
+      <c r="Q34" s="18"/>
+    </row>
+    <row r="35" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="113"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="112"/>
+      <c r="L35" s="12"/>
+      <c r="Q35" s="18"/>
+    </row>
+    <row r="36" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A37" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A38" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A39" t="s">
+        <v>227</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="G1:Q3"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/monolith-to-microservice-architecture-uionly-stack-a-b-c/microservice-architecture/microservice-architecture-update-02022026.xlsx
+++ b/monolith-to-microservice-architecture-uionly-stack-a-b-c/microservice-architecture/microservice-architecture-update-02022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\monolith-to-microservice-architecture-uionly-stack-a-b-c\microservice-architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B1BCD0-28BB-48FA-A0EA-82F94E3E28B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DE03B5-2B88-42BB-98E3-4B72E17DA1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="256">
   <si>
     <t>Part</t>
   </si>
@@ -877,48 +877,34 @@
     <t>Authentication - Backend Stack</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Mql5 (EA)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for market data fetching from MT5 terminals + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Python Stacks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for Retry/Recover/Resend machanism</t>
-    </r>
+    <t>Notifications &amp; Real-time</t>
+  </si>
+  <si>
+    <t>v2_29_data_pipeline_architecture</t>
+  </si>
+  <si>
+    <t>v2_29_multi-timeframe-visualisation</t>
+  </si>
+  <si>
+    <t>drawing-engine-line-alerts</t>
+  </si>
+  <si>
+    <t>Next.js V14 is refactored to Nest.js V11</t>
+  </si>
+  <si>
+    <t>79 fields, centroid-regression/EDT schema</t>
+  </si>
+  <si>
+    <t>Prisma Schema in Contabo VPS + SQLite in Contabo VPS</t>
+  </si>
+  <si>
+    <t>Prisma Schema : market_data_v6</t>
+  </si>
+  <si>
+    <t>Database Stack</t>
+  </si>
+  <si>
+    <t>Next.js V15.5.7 is refactored to Nest.js V11</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1671,13 +1657,34 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6412,7 +6419,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D501F09-0F51-4028-AA61-070B2DDA5F82}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="28.3984375" customWidth="1"/>
@@ -6640,7 +6647,7 @@
       <c r="P11" s="9"/>
       <c r="Q11" s="10"/>
     </row>
-    <row r="12" spans="1:17" s="11" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:17" s="11" customFormat="1" ht="56.7" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="7" t="s">
         <v>7</v>
       </c>
@@ -6661,16 +6668,16 @@
         <v>7</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="I12" s="73" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="L12" s="32"/>
       <c r="M12" s="19" t="s">
@@ -6763,7 +6770,7 @@
         <v>222</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>126</v>
@@ -6880,19 +6887,19 @@
         <v>234</v>
       </c>
       <c r="F17" s="39"/>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="73" t="s">
+      <c r="I17" s="115" t="s">
         <v>222</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="J17" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="45" t="s">
         <v>126</v>
       </c>
       <c r="L17" s="33"/>
@@ -6939,7 +6946,7 @@
         <v>222</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>126</v>
@@ -6988,7 +6995,7 @@
         <v>222</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>126</v>
@@ -7037,7 +7044,7 @@
         <v>222</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>126</v>
@@ -7086,7 +7093,7 @@
         <v>222</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>126</v>
@@ -7135,7 +7142,7 @@
         <v>222</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>126</v>
@@ -7174,19 +7181,19 @@
         <v>233</v>
       </c>
       <c r="F23" s="39"/>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="73" t="s">
+      <c r="I23" s="114" t="s">
         <v>222</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="K23" s="9" t="s">
+      <c r="J23" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K23" s="43" t="s">
         <v>126</v>
       </c>
       <c r="L23" s="33"/>
@@ -7233,7 +7240,7 @@
         <v>222</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>126</v>
@@ -7282,7 +7289,7 @@
         <v>222</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>126</v>
@@ -7309,7 +7316,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="C26" s="73" t="s">
         <v>97</v>
@@ -7325,13 +7332,13 @@
         <v>34</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="I26" s="73" t="s">
         <v>222</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>126</v>
@@ -7380,7 +7387,7 @@
         <v>222</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>126</v>
@@ -7419,19 +7426,19 @@
         <v>233</v>
       </c>
       <c r="F28" s="39"/>
-      <c r="G28" s="114" t="s">
+      <c r="G28" s="118" t="s">
         <v>60</v>
       </c>
-      <c r="H28" s="115" t="s">
+      <c r="H28" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="116" t="s">
+      <c r="I28" s="114" t="s">
         <v>222</v>
       </c>
-      <c r="J28" s="115" t="s">
-        <v>238</v>
-      </c>
-      <c r="K28" s="115" t="s">
+      <c r="J28" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K28" s="43" t="s">
         <v>126</v>
       </c>
       <c r="L28" s="33"/>
@@ -7468,19 +7475,19 @@
         <v>233</v>
       </c>
       <c r="F29" s="39"/>
-      <c r="G29" s="114" t="s">
+      <c r="G29" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="H29" s="115" t="s">
+      <c r="H29" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="I29" s="116" t="s">
+      <c r="I29" s="114" t="s">
         <v>222</v>
       </c>
-      <c r="J29" s="115" t="s">
-        <v>238</v>
-      </c>
-      <c r="K29" s="115" t="s">
+      <c r="J29" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K29" s="43" t="s">
         <v>126</v>
       </c>
       <c r="L29" s="33"/>
@@ -7515,19 +7522,19 @@
         <v>233</v>
       </c>
       <c r="F30" s="39"/>
-      <c r="G30" s="114" t="s">
+      <c r="G30" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="115" t="s">
+      <c r="H30" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="116" t="s">
+      <c r="I30" s="114" t="s">
         <v>222</v>
       </c>
-      <c r="J30" s="115" t="s">
-        <v>238</v>
-      </c>
-      <c r="K30" s="115" t="s">
+      <c r="J30" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K30" s="43" t="s">
         <v>126</v>
       </c>
       <c r="L30" s="33"/>
@@ -7564,19 +7571,19 @@
         <v>233</v>
       </c>
       <c r="F31" s="39"/>
-      <c r="G31" s="114" t="s">
+      <c r="G31" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="H31" s="115" t="s">
+      <c r="H31" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="I31" s="116" t="s">
+      <c r="I31" s="114" t="s">
         <v>222</v>
       </c>
-      <c r="J31" s="115" t="s">
-        <v>238</v>
-      </c>
-      <c r="K31" s="115" t="s">
+      <c r="J31" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="K31" s="43" t="s">
         <v>126</v>
       </c>
       <c r="L31" s="33"/>
@@ -7596,118 +7603,144 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="11" customFormat="1" ht="27.3" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="108"/>
-      <c r="B32" s="109"/>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
+    <row r="32" spans="1:17" s="11" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="110"/>
+      <c r="B32" s="111"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
       <c r="F32" s="106"/>
-      <c r="G32" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="I32" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L32" s="12"/>
-      <c r="Q32" s="18"/>
-    </row>
-    <row r="33" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="G32" s="14"/>
+      <c r="H32" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I32" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="K32" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="L32" s="120"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="119"/>
+      <c r="O32" s="119"/>
+      <c r="P32" s="119"/>
+      <c r="Q32" s="122"/>
+    </row>
+    <row r="33" spans="1:17" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A33" s="108"/>
       <c r="B33" s="109"/>
       <c r="C33" s="109"/>
       <c r="D33" s="109"/>
       <c r="E33" s="109"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" s="78" t="s">
-        <v>86</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>246</v>
-      </c>
+      <c r="F33" s="106"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="I33" s="80"/>
+      <c r="J33" s="9"/>
       <c r="K33" s="9" t="s">
         <v>127</v>
       </c>
       <c r="L33" s="12"/>
       <c r="Q33" s="18"/>
     </row>
-    <row r="34" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="51"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="I34" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="K34" s="83" t="s">
-        <v>128</v>
+    <row r="34" spans="1:17" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="108"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="L34" s="12"/>
       <c r="Q34" s="18"/>
     </row>
-    <row r="35" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="51"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="110"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="113"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="112"/>
+    <row r="35" spans="1:17" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="108"/>
+      <c r="B35" s="109"/>
+      <c r="C35" s="109"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="107"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I35" s="78"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9" t="s">
+        <v>127</v>
+      </c>
       <c r="L35" s="12"/>
       <c r="Q35" s="18"/>
     </row>
-    <row r="36" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="54" t="s">
+    <row r="36" spans="1:17" s="11" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I36" s="77"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="83" t="s">
+        <v>126</v>
+      </c>
+      <c r="L36" s="12"/>
+      <c r="Q36" s="18"/>
+    </row>
+    <row r="37" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A37" s="51"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="110"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="113"/>
+      <c r="J37" s="111"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="12"/>
+      <c r="Q37" s="18"/>
+    </row>
+    <row r="38" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="A37" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="A38" t="s">
-        <v>226</v>
-      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.6">
       <c r="A39" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A41" t="s">
         <v>227</v>
       </c>
     </row>
@@ -7723,6 +7756,9 @@
     <mergeCell ref="E15:E16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup scale="96" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="6" max="40" man="1"/>
+  </colBreaks>
 </worksheet>
 </file>
--- a/monolith-to-microservice-architecture-uionly-stack-a-b-c/microservice-architecture/microservice-architecture-update-02022026.xlsx
+++ b/monolith-to-microservice-architecture-uionly-stack-a-b-c/microservice-architecture/microservice-architecture-update-02022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\monolith-to-microservice-architecture-uionly-stack-a-b-c\microservice-architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DE03B5-2B88-42BB-98E3-4B72E17DA1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2DB35B-CBC9-40E6-86C4-6B093150B1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="255">
   <si>
     <t>Part</t>
   </si>
@@ -887,9 +887,6 @@
   </si>
   <si>
     <t>drawing-engine-line-alerts</t>
-  </si>
-  <si>
-    <t>Next.js V14 is refactored to Nest.js V11</t>
   </si>
   <si>
     <t>79 fields, centroid-regression/EDT schema</t>
@@ -1216,7 +1213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1333,20 +1330,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1633,18 +1621,6 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1683,9 +1659,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6419,331 +6392,272 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D501F09-0F51-4028-AA61-070B2DDA5F82}">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="2" max="2" width="28.3984375" customWidth="1"/>
-    <col min="3" max="5" width="12.8984375" customWidth="1"/>
-    <col min="6" max="6" width="0.6484375" customWidth="1"/>
-    <col min="7" max="7" width="7.34765625" customWidth="1"/>
-    <col min="8" max="8" width="32.59765625" customWidth="1"/>
-    <col min="9" max="9" width="13.75" customWidth="1"/>
-    <col min="10" max="10" width="32.69921875" customWidth="1"/>
-    <col min="11" max="11" width="13.6484375" customWidth="1"/>
-    <col min="12" max="12" width="23.546875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.94921875" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="75.19921875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="5.75" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="81.25" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="5.796875" style="1" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="7.34765625" customWidth="1"/>
+    <col min="2" max="2" width="32.59765625" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="32.69921875" customWidth="1"/>
+    <col min="5" max="5" width="13.6484375" customWidth="1"/>
+    <col min="6" max="6" width="23.546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.94921875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="75.19921875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.75" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="81.25" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="5.796875" style="1" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
-      <c r="G1" s="84" t="s">
+    <row r="1" spans="1:11" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="84" t="s">
         <v>75</v>
       </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="84"/>
       <c r="I1" s="84"/>
       <c r="J1" s="84"/>
       <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-    </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
       <c r="G2" s="84"/>
       <c r="H2" s="84"/>
       <c r="I2" s="84"/>
       <c r="J2" s="84"/>
       <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-    </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
       <c r="G3" s="84"/>
       <c r="H3" s="84"/>
       <c r="I3" s="84"/>
       <c r="J3" s="84"/>
       <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-    </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" s="5">
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="G5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="G6" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="G7" s="3"/>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:11" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="G8" s="3"/>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="4"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="G9" s="3"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" ht="20.05" hidden="1" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="29"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="90" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" s="90"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="92" t="s">
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="34" t="s">
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" s="35" t="s">
+      <c r="D11" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" s="36" t="s">
+      <c r="E11" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="10"/>
-    </row>
-    <row r="12" spans="1:17" s="11" customFormat="1" ht="56.7" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="F11" s="31"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" s="11" customFormat="1" ht="56.7" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="7" t="s">
-        <v>7</v>
+        <v>253</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" s="32"/>
+      <c r="G12" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="I12" s="73" t="s">
-        <v>254</v>
-      </c>
-      <c r="J12" s="43" t="s">
-        <v>251</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="L12" s="32"/>
-      <c r="M12" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="J12" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="K12" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="11" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:11" s="11" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="7" t="s">
-        <v>9</v>
+      <c r="C13" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="74" t="s">
-        <v>122</v>
+        <v>11</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="K13" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:11" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
@@ -6751,175 +6665,121 @@
         <v>13</v>
       </c>
       <c r="C14" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="7" t="s">
-        <v>12</v>
+        <v>222</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="33"/>
+      <c r="G14" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="11" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="33"/>
+      <c r="G15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="11" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="33"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="112" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="111" t="s">
         <v>222</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="K14" s="9" t="s">
+      <c r="D17" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="L14" s="33"/>
-      <c r="M14" s="19" t="s">
+      <c r="F17" s="33"/>
+      <c r="G17" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O14" s="7" t="s">
+      <c r="H17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="J17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="K17" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="11" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="104" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="100" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="100" t="s">
-        <v>233</v>
-      </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="I15" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="L15" s="33"/>
-      <c r="M15" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" s="11" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="101"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="I16" s="76" t="s">
-        <v>229</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L16" s="33"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="10"/>
-    </row>
-    <row r="17" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="116" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="115" t="s">
-        <v>222</v>
-      </c>
-      <c r="J17" s="45" t="s">
-        <v>234</v>
-      </c>
-      <c r="K17" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="L17" s="33"/>
-      <c r="M17" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A18" s="7" t="s">
         <v>20</v>
       </c>
@@ -6927,48 +6787,32 @@
         <v>95</v>
       </c>
       <c r="C18" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="7" t="s">
-        <v>20</v>
+        <v>222</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="33"/>
+      <c r="G18" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I18" s="73" t="s">
-        <v>222</v>
+        <v>21</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L18" s="33"/>
-      <c r="M18" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="P18" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="K18" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A19" s="7" t="s">
         <v>40</v>
       </c>
@@ -6976,48 +6820,32 @@
         <v>42</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="7" t="s">
-        <v>40</v>
+        <v>222</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="33"/>
+      <c r="G19" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>222</v>
+        <v>49</v>
+      </c>
+      <c r="I19" s="7">
+        <v>3</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L19" s="33"/>
-      <c r="M19" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="O19" s="7">
-        <v>3</v>
-      </c>
-      <c r="P19" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="K19" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A20" s="7" t="s">
         <v>41</v>
       </c>
@@ -7025,48 +6853,32 @@
         <v>43</v>
       </c>
       <c r="C20" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="7" t="s">
-        <v>41</v>
+        <v>222</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="33"/>
+      <c r="G20" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="73" t="s">
-        <v>222</v>
+        <v>50</v>
+      </c>
+      <c r="I20" s="7">
+        <v>2</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L20" s="33"/>
-      <c r="M20" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="O20" s="7">
-        <v>2</v>
-      </c>
-      <c r="P20" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="Q20" s="10">
+      <c r="K20" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="11" customFormat="1" ht="21.3" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:11" s="11" customFormat="1" ht="21.3" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
@@ -7074,48 +6886,32 @@
         <v>23</v>
       </c>
       <c r="C21" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="7" t="s">
-        <v>22</v>
+        <v>222</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="G21" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="73" t="s">
-        <v>222</v>
+        <v>51</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L21" s="33"/>
-      <c r="M21" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P21" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q21" s="10">
+      <c r="K21" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:11" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A22" s="7" t="s">
         <v>25</v>
       </c>
@@ -7123,97 +6919,65 @@
         <v>26</v>
       </c>
       <c r="C22" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="7" t="s">
-        <v>25</v>
+        <v>222</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="113" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="110" t="s">
         <v>222</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K22" s="9" t="s">
+      <c r="D23" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E23" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="L22" s="33"/>
-      <c r="M22" s="19" t="s">
+      <c r="F23" s="33"/>
+      <c r="G23" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="N22" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="82" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="J23" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="K23" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="L23" s="33"/>
-      <c r="M23" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="O23" s="14" t="s">
+      <c r="I23" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="J23" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="K23" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="7" t="s">
         <v>30</v>
       </c>
@@ -7221,48 +6985,32 @@
         <v>31</v>
       </c>
       <c r="C24" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="7" t="s">
-        <v>30</v>
+        <v>222</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="33"/>
+      <c r="G24" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="73" t="s">
-        <v>222</v>
+        <v>54</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L24" s="33"/>
-      <c r="M24" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P24" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="K24" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="7" t="s">
         <v>32</v>
       </c>
@@ -7270,48 +7018,32 @@
         <v>33</v>
       </c>
       <c r="C25" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F25" s="39"/>
-      <c r="G25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I25" s="73" t="s">
         <v>222</v>
       </c>
+      <c r="D25" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="33"/>
+      <c r="G25" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="17">
+        <v>3</v>
+      </c>
       <c r="J25" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L25" s="33"/>
-      <c r="M25" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="O25" s="17">
-        <v>3</v>
-      </c>
-      <c r="P25" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="Q25" s="10">
+      <c r="K25" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:11" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A26" s="7" t="s">
         <v>34</v>
       </c>
@@ -7319,48 +7051,32 @@
         <v>246</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F26" s="39"/>
-      <c r="G26" s="7" t="s">
-        <v>34</v>
+        <v>222</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" s="33"/>
+      <c r="G26" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="I26" s="73" t="s">
-        <v>222</v>
+        <v>35</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="L26" s="33"/>
-      <c r="M26" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P26" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="Q26" s="10">
+      <c r="K26" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
@@ -7368,397 +7084,254 @@
         <v>37</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F27" s="39"/>
-      <c r="G27" s="7" t="s">
-        <v>36</v>
+        <v>222</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="33"/>
+      <c r="G27" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I27" s="73" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K27" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="114" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="110" t="s">
         <v>222</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K27" s="9" t="s">
+      <c r="D28" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E28" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="L27" s="33"/>
-      <c r="M27" s="19" t="s">
+      <c r="F28" s="33"/>
+      <c r="G28" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="N27" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q27" s="10">
+      <c r="H28" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="114" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="110" t="s">
+        <v>222</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" s="33"/>
+      <c r="G29" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="114" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="110" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="F30" s="33"/>
+      <c r="G30" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F28" s="39"/>
-      <c r="G28" s="118" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="I28" s="114" t="s">
+    <row r="31" spans="1:11" s="11" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="114" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="110" t="s">
         <v>222</v>
       </c>
-      <c r="J28" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="K28" s="43" t="s">
+      <c r="D31" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="L28" s="33"/>
-      <c r="M28" s="19" t="s">
+      <c r="F31" s="33"/>
+      <c r="G31" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="N28" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q28" s="10">
+      <c r="H31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="118" t="s">
-        <v>62</v>
-      </c>
-      <c r="H29" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="I29" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="J29" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="K29" s="43" t="s">
+      <c r="J31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="11" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="14"/>
+      <c r="B32" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>223</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="E32" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="116"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="115"/>
+      <c r="J32" s="115"/>
+      <c r="K32" s="118"/>
+    </row>
+    <row r="33" spans="1:11" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="7"/>
+      <c r="B33" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C33" s="80"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="K33" s="18"/>
+    </row>
+    <row r="34" spans="1:11" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="7"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="K34" s="18"/>
+    </row>
+    <row r="35" spans="1:11" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="7"/>
+      <c r="B35" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C35" s="78"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="K35" s="18"/>
+    </row>
+    <row r="36" spans="1:11" s="11" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="14"/>
+      <c r="B36" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="77"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="83" t="s">
         <v>126</v>
       </c>
-      <c r="L29" s="33"/>
-      <c r="M29" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="O29" s="7"/>
-      <c r="P29" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="11" customFormat="1" ht="20.05" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="118" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="I30" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="J30" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="K30" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="L30" s="33"/>
-      <c r="M30" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" s="11" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="F31" s="39"/>
-      <c r="G31" s="118" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" s="114" t="s">
-        <v>222</v>
-      </c>
-      <c r="J31" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="K31" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="L31" s="33"/>
-      <c r="M31" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="O31" s="7">
-        <v>0</v>
-      </c>
-      <c r="P31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q31" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" s="11" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A32" s="110"/>
-      <c r="B32" s="111"/>
-      <c r="C32" s="123"/>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="I32" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="K32" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="L32" s="120"/>
-      <c r="M32" s="121"/>
-      <c r="N32" s="119"/>
-      <c r="O32" s="119"/>
-      <c r="P32" s="119"/>
-      <c r="Q32" s="122"/>
-    </row>
-    <row r="33" spans="1:17" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="108"/>
-      <c r="B33" s="109"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="I33" s="80"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="L33" s="12"/>
-      <c r="Q33" s="18"/>
-    </row>
-    <row r="34" spans="1:17" s="11" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="108"/>
-      <c r="B34" s="109"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="L34" s="12"/>
-      <c r="Q34" s="18"/>
-    </row>
-    <row r="35" spans="1:17" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="108"/>
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I35" s="78"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="L35" s="12"/>
-      <c r="Q35" s="18"/>
-    </row>
-    <row r="36" spans="1:17" s="11" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="I36" s="77"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="83" t="s">
-        <v>126</v>
-      </c>
-      <c r="L36" s="12"/>
-      <c r="Q36" s="18"/>
-    </row>
-    <row r="37" spans="1:17" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A37" s="51"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="110"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="113"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="12"/>
-      <c r="Q37" s="18"/>
-    </row>
-    <row r="38" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A38" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="A39" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="A40" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.6">
-      <c r="A41" t="s">
-        <v>227</v>
-      </c>
+      <c r="F36" s="12"/>
+      <c r="K36" s="18"/>
+    </row>
+    <row r="37" spans="1:11" s="11" customFormat="1" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A37" s="106"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="109"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="12"/>
+      <c r="K37" s="18"/>
+    </row>
+    <row r="38" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G1:Q3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K3"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="96" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="6" max="40" man="1"/>
-  </colBreaks>
 </worksheet>
 </file>